--- a/data/trans_orig/IQ09_A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_A-Clase-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio en años que llevan sufriendo esa dolencia, enfermedad o impedimento que les haya limitado de forma continuada (más de 10 días en los últimos 12 meses)</t>
+          <t>Tiempo medio en años que llevan sufriendo esa dolencia, enfermedad o impedimento que les haya limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 97,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 6,61</t>
+          <t>2,07; 6,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,13</t>
+          <t>0,2; 3,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 6,38</t>
+          <t>0,43; 6,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,75</t>
+          <t>0,27; 2,46</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,5</t>
+          <t>0,51; 5,95</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,5; 6,46</t>
+          <t>2,49; 6,64</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,96</t>
+          <t>0,0; 5,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 9,25</t>
+          <t>1,39; 9,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 7,29</t>
+          <t>1,2; 7,19</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 12,86</t>
+          <t>0,2; 12,94</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 11,52</t>
+          <t>1,4; 11,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 7,0</t>
+          <t>0,0; 5,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 11,52</t>
+          <t>1,4; 11,01</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,84</t>
+          <t>0,0; 6,16</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 5,28</t>
+          <t>0,24; 4,79</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,91</t>
+          <t>0,22; 2,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,46</t>
+          <t>0,92; 4,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,47</t>
+          <t>0,0; 3,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,86</t>
+          <t>0,26; 2,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,66</t>
+          <t>0,0; 10,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 5,07</t>
+          <t>1,53; 5,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,77</t>
+          <t>0,0; 2,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,6</t>
+          <t>1,23; 5,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 5,87</t>
+          <t>0,72; 5,68</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,98</t>
+          <t>1,57; 4,13</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,2</t>
+          <t>0,25; 2,45</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,95</t>
+          <t>1,34; 3,73</t>
         </is>
       </c>
     </row>
@@ -1281,27 +1281,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,01</t>
+          <t>0,91; 4,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 5,62</t>
+          <t>1,16; 5,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 7,49</t>
+          <t>1,13; 7,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,6</t>
+          <t>0,79; 3,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 6,22</t>
+          <t>1,11; 6,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1311,27 +1311,27 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 6,91</t>
+          <t>1,01; 6,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 6,93</t>
+          <t>1,66; 6,77</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,42</t>
+          <t>1,39; 4,6</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,45</t>
+          <t>1,33; 5,41</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,96</t>
+          <t>1,83; 6,08</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,41; 11,7</t>
+          <t>0,68; 11,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,52</t>
+          <t>0,0; 7,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,52</t>
+          <t>0,0; 9,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,33</t>
+          <t>0,0; 4,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,45; 5,89</t>
+          <t>1,89; 6,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,86; 5,41</t>
+          <t>0,88; 5,27</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,94; 8,04</t>
+          <t>1,57; 8,0</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,9</t>
+          <t>0,0; 3,82</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,66; 8,16</t>
+          <t>2,92; 8,02</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 5,29</t>
+          <t>1,19; 5,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,1</t>
+          <t>1,26; 3,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,12</t>
+          <t>0,85; 3,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,94; 4,64</t>
+          <t>1,91; 4,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,82</t>
+          <t>1,93; 5,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,19</t>
+          <t>1,71; 4,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,77</t>
+          <t>1,44; 3,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,82; 6,01</t>
+          <t>2,74; 6,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,42</t>
+          <t>1,94; 4,17</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,79; 3,45</t>
+          <t>1,8; 3,53</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,13</t>
+          <t>1,38; 3,14</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,76; 4,98</t>
+          <t>2,7; 4,92</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ09_A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_A-Clase-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,07; 6,85</t>
+          <t>1,94; 6,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 3,19</t>
+          <t>0,2; 3,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 6,44</t>
+          <t>0,44; 6,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,46</t>
+          <t>0,27; 2,47</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,95</t>
+          <t>0,51; 5,79</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,49; 6,64</t>
+          <t>2,47; 6,56</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,39; 9,4</t>
+          <t>1,25; 9,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 7,19</t>
+          <t>1,21; 6,71</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 12,94</t>
+          <t>0,19; 12,58</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 11,01</t>
+          <t>1,8; 11,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 11,01</t>
+          <t>1,8; 11,52</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 4,79</t>
+          <t>0,27; 4,8</t>
         </is>
       </c>
     </row>
@@ -1141,57 +1141,57 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,73</t>
+          <t>0,91; 4,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,52</t>
+          <t>0,0; 3,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,88</t>
+          <t>0,24; 2,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,28</t>
+          <t>0,0; 10,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 5,02</t>
+          <t>1,65; 5,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,83</t>
+          <t>0,0; 3,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 5,55</t>
+          <t>1,29; 5,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 5,68</t>
+          <t>0,73; 6,01</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,13</t>
+          <t>1,59; 4,09</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,45</t>
+          <t>0,24; 2,38</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,73</t>
+          <t>1,36; 3,78</t>
         </is>
       </c>
     </row>
@@ -1281,12 +1281,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,42</t>
+          <t>0,88; 4,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 5,88</t>
+          <t>1,16; 5,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1296,12 +1296,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,72</t>
+          <t>0,8; 3,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 6,09</t>
+          <t>1,06; 6,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1311,27 +1311,27 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 6,53</t>
+          <t>0,99; 7,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 6,77</t>
+          <t>1,76; 7,13</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,6</t>
+          <t>1,4; 4,54</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,33; 5,41</t>
+          <t>1,26; 5,16</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,83; 6,08</t>
+          <t>1,66; 5,97</t>
         </is>
       </c>
     </row>
@@ -1436,42 +1436,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,76</t>
+          <t>0,0; 7,52</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,66</t>
+          <t>0,0; 9,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,04</t>
+          <t>0,0; 4,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,89; 6,07</t>
+          <t>1,64; 5,87</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,27</t>
+          <t>0,91; 5,42</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,57; 8,0</t>
+          <t>1,93; 8,02</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,82</t>
+          <t>0,0; 3,84</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,92; 8,02</t>
+          <t>2,87; 8,21</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,29</t>
+          <t>1,28; 5,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,12</t>
+          <t>1,23; 3,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,15</t>
+          <t>0,84; 3,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,54</t>
+          <t>2,1; 4,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,93; 5,07</t>
+          <t>1,89; 4,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,71; 4,37</t>
+          <t>1,81; 4,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,92</t>
+          <t>1,41; 4,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,74; 6,01</t>
+          <t>2,78; 6,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,94; 4,17</t>
+          <t>1,91; 4,1</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,53</t>
+          <t>1,79; 3,44</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,14</t>
+          <t>1,29; 3,0</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,7; 4,92</t>
+          <t>2,83; 5,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ09_A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_A-Clase-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,54 +648,54 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,02</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4,67</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>0,94</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1,0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,13</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,02</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4,24</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1,0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,1</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4,75</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1,0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
           <t>1,96</t>
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,37</t>
+          <t>4,39</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 3,13</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0,42; 6,38</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1,32; 8,99</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>0,0; 2,0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1,94; 6,88</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,2; 3,23</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2,0; 6,82</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0,27; 2,75</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,44; 6,31</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1,65; 8,76</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0,27; 2,47</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,79</t>
+          <t>0,51; 5,5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,47; 6,56</t>
+          <t>2,4; 6,51</t>
         </is>
       </c>
     </row>
@@ -788,49 +788,49 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2,67</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4,0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8,83</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,98</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>1,41</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>2,67</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4,0</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8,5</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2,67</t>
-        </is>
-      </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0,7</t>
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,19</t>
+          <t>5,44</t>
         </is>
       </c>
     </row>
@@ -856,49 +856,49 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 6,74</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1,48; 9,25</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0,33; 14,79</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>0,0; 3,0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 3,96</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>0,0; 6,74</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,25; 9,62</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0,32; 14,77</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,74</t>
-        </is>
-      </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0,0; 2,28</t>
@@ -906,12 +906,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 6,71</t>
+          <t>1,21; 7,29</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 12,58</t>
+          <t>0,2; 13,08</t>
         </is>
       </c>
     </row>
@@ -928,49 +928,49 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6,28</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6,46</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2,48</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,98</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,84</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0,75</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>6,28</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6,46</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2,75</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>6,28</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0,75</t>
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,16</t>
+          <t>1,91</t>
         </is>
       </c>
     </row>
@@ -996,47 +996,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>1,61; 11,52</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>5,0; 8,0</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 5,58</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>0,0; 3,0</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>0,0; 2,0</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1,8; 11,52</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>5,0; 8,0</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,56</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 11,52</t>
+          <t>1,61; 11,52</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,16</t>
+          <t>0,0; 5,84</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 4,8</t>
+          <t>0,36; 5,31</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,18</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2,93</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,73</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2,84</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1,27</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,11</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,28</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,01</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,18</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,93</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,73</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,96</t>
+          <t>1,02</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,44</t>
+          <t>2,12</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,83</t>
+          <t>0,0; 10,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,72</t>
+          <t>1,53; 5,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,29</t>
+          <t>0,0; 2,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,88</t>
+          <t>1,28; 5,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,43</t>
+          <t>0,22; 2,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 5,19</t>
+          <t>0,91; 4,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,0</t>
+          <t>0,0; 3,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,51</t>
+          <t>0,18; 2,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,01</t>
+          <t>0,77; 5,87</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 4,09</t>
+          <t>1,64; 3,98</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,38</t>
+          <t>0,23; 2,2</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,78</t>
+          <t>1,05; 4,25</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,1</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,93</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,92</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3,55</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>7,69</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2,2</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>2,57</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,46</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,1</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,93</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,92</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,28</t>
+          <t>4,61</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,66</t>
+          <t>3,92</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0,81; 3,6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1,18; 6,22</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0,32; 4,0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0,89; 7,17</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>0,0; 12,67</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0,88; 4,34</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1,16; 5,9</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1,13; 7,69</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,8; 3,58</t>
-        </is>
-      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,06; 6,17</t>
+          <t>0,87; 4,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 4,0</t>
+          <t>1,16; 5,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 7,01</t>
+          <t>1,08; 7,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 7,13</t>
+          <t>1,63; 6,93</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 4,54</t>
+          <t>1,45; 4,42</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,26; 5,16</t>
+          <t>1,3; 5,45</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 5,97</t>
+          <t>2,01; 6,22</t>
         </is>
       </c>
     </row>
@@ -1348,42 +1348,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3,68</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4,72</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4,0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>1,84</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>3,38</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6,74</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>3,68</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4,72</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,5</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4,07</t>
+          <t>7,58</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,11</t>
+          <t>5,43</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>0,0; 7,52</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 9,52</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0,38; 4,33</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1,35; 5,9</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>0,0; 3,1</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>2,0; 4,0</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>0,68; 11,7</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,52</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 9,52</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,23</t>
-        </is>
-      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,64; 5,87</t>
+          <t>0,67; 12,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,42</t>
+          <t>0,86; 5,41</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,93; 8,02</t>
+          <t>1,94; 8,04</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,84</t>
+          <t>0,0; 3,9</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,87; 8,21</t>
+          <t>2,81; 8,73</t>
         </is>
       </c>
     </row>
@@ -1488,42 +1488,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3,06</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2,85</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2,35</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4,2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>2,56</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1,96</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>1,6</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,1</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3,06</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,85</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,35</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>4,11</t>
+          <t>3,32</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,65</t>
+          <t>3,83</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,28; 5,22</t>
+          <t>1,79; 4,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,08</t>
+          <t>1,66; 4,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,24</t>
+          <t>1,35; 3,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,72</t>
+          <t>2,84; 6,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,99</t>
+          <t>1,21; 5,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,36</t>
+          <t>1,2; 3,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,04</t>
+          <t>0,87; 3,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,78; 6,01</t>
+          <t>1,88; 5,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,1</t>
+          <t>2,01; 4,42</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,79; 3,44</t>
+          <t>1,79; 3,45</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,0</t>
+          <t>1,35; 3,13</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,83; 5,05</t>
+          <t>2,8; 5,31</t>
         </is>
       </c>
     </row>
